--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC563CB3-8AA2-4F32-9732-30F0D5100D31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="114">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -328,13 +328,75 @@
   </si>
   <si>
     <t>Yes — revisit in DP</t>
+  </si>
+  <si>
+    <t>Majority Element II</t>
+  </si>
+  <si>
+    <t>Generalized Boyer-Moore / Frequency Counting</t>
+  </si>
+  <si>
+    <t>Moore / Frequency Counting
+For each element, count occurrences with another loop → O(n²) time, O(1) space</t>
+  </si>
+  <si>
+    <t>HashMap frequency counting → O(n) time, O(n) space</t>
+  </si>
+  <si>
+    <t>Generalized Boyer-Moore Voting + verification → O(n) time, O(1) space</t>
+  </si>
+  <si>
+    <t>Subarray Sum Equals K</t>
+  </si>
+  <si>
+    <t>Prefix Sum + HashMap</t>
+  </si>
+  <si>
+    <t>Generate every subarray and calculate its sum → O(n²) time, O(1) space</t>
+  </si>
+  <si>
+    <t>Prefix Sum + search previous prefix sums → O(n²) time, O(n) space</t>
+  </si>
+  <si>
+    <t>Prefix Sum + HashMap frequency → O(n) average time, O(n) space</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>First Missing Positive</t>
+  </si>
+  <si>
+    <t>In-place Index Marking / Cyclic Placement</t>
+  </si>
+  <si>
+    <t>Check each positive integer 1, 2, 3... using a scan → O(n²), O(1)</t>
+  </si>
+  <si>
+    <t>HashSet → O(n) average, O(n)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In-place index/sign marking → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n), O(1)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,6 +417,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -364,7 +434,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -387,11 +457,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -400,6 +481,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -417,6 +513,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -746,9 +846,10 @@
     <col min="6" max="6" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="19.109375" customWidth="1"/>
     <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -773,8 +874,11 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="I1" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>38565</v>
       </c>
@@ -800,7 +904,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>38930</v>
       </c>
@@ -826,7 +930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>39295</v>
       </c>
@@ -852,7 +956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>39661</v>
       </c>
@@ -878,7 +982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>39661</v>
       </c>
@@ -904,7 +1008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>39661</v>
       </c>
@@ -930,7 +1034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>39661</v>
       </c>
@@ -955,8 +1059,11 @@
       <c r="H8" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>40026</v>
       </c>
@@ -982,7 +1089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>40026</v>
       </c>
@@ -1008,7 +1115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>40391</v>
       </c>
@@ -1033,8 +1140,11 @@
       <c r="H11" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>40756</v>
       </c>
@@ -1059,8 +1169,11 @@
       <c r="H12" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>41487</v>
       </c>
@@ -1085,8 +1198,11 @@
       <c r="H13" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="I13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>41487</v>
       </c>
@@ -1112,7 +1228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>41852</v>
       </c>
@@ -1138,7 +1254,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>42217</v>
       </c>
@@ -1164,7 +1280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>42217</v>
       </c>
@@ -1190,7 +1306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>42948</v>
       </c>
@@ -1216,7 +1332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>43313</v>
       </c>
@@ -1240,6 +1356,90 @@
       </c>
       <c r="H19" s="2" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>43313</v>
+      </c>
+      <c r="B20" s="2">
+        <v>229</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>43678</v>
+      </c>
+      <c r="B21" s="2">
+        <v>560</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>44044</v>
+      </c>
+      <c r="B22" s="2">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC563CB3-8AA2-4F32-9732-30F0D5100D31}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7AC9B3-383F-4AF1-8DF4-7F8517BD047A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="123">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -389,6 +389,289 @@
         <scheme val="minor"/>
       </rPr>
       <t>O(n), O(1)</t>
+    </r>
+  </si>
+  <si>
+    <t>Valid Palindrome II</t>
+  </si>
+  <si>
+    <t>Two Pointers + Greedy / At Most One Deletion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Try deleting each character and check palindrome → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two pointers + create/check substrings after mismatch → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two pointers; at first mismatch, check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>skip-left</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> OR </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>skip-right</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Merge sorted array</t>
+  </si>
+  <si>
+    <t>Two Pointers / In-place Merge from Back</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Merge using a separate array → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(m+n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(m+n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Merge from front with shifting elements → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(m·n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
     </r>
   </si>
 </sst>
@@ -396,7 +679,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +707,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -836,8 +1124,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
@@ -849,7 +1137,7 @@
     <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="29.4" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -878,7 +1166,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="57.6">
       <c r="A2" s="3">
         <v>38565</v>
       </c>
@@ -904,7 +1192,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="43.2">
       <c r="A3" s="3">
         <v>38930</v>
       </c>
@@ -930,7 +1218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="57.6">
       <c r="A4" s="3">
         <v>39295</v>
       </c>
@@ -956,7 +1244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="57.6">
       <c r="A5" s="3">
         <v>39661</v>
       </c>
@@ -982,7 +1270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="57.6">
       <c r="A6" s="3">
         <v>39661</v>
       </c>
@@ -1008,7 +1296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="43.2">
       <c r="A7" s="3">
         <v>39661</v>
       </c>
@@ -1034,7 +1322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="43.2">
       <c r="A8" s="3">
         <v>39661</v>
       </c>
@@ -1063,7 +1351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="43.2">
       <c r="A9" s="3">
         <v>40026</v>
       </c>
@@ -1089,7 +1377,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="43.2">
       <c r="A10" s="3">
         <v>40026</v>
       </c>
@@ -1115,7 +1403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="57.6">
       <c r="A11" s="3">
         <v>40391</v>
       </c>
@@ -1144,7 +1432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="43.2">
       <c r="A12" s="3">
         <v>40756</v>
       </c>
@@ -1173,7 +1461,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="43.2">
       <c r="A13" s="3">
         <v>41487</v>
       </c>
@@ -1202,7 +1490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="72">
       <c r="A14" s="3">
         <v>41487</v>
       </c>
@@ -1228,7 +1516,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="43.2">
       <c r="A15" s="3">
         <v>41852</v>
       </c>
@@ -1254,7 +1542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="57.6">
       <c r="A16" s="3">
         <v>42217</v>
       </c>
@@ -1280,7 +1568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="72">
       <c r="A17" s="3">
         <v>42217</v>
       </c>
@@ -1306,7 +1594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="57.6">
       <c r="A18" s="3">
         <v>42948</v>
       </c>
@@ -1332,7 +1620,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="72">
       <c r="A19" s="3">
         <v>43313</v>
       </c>
@@ -1358,7 +1646,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="100.8">
       <c r="A20" s="3">
         <v>43313</v>
       </c>
@@ -1384,7 +1672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="72">
       <c r="A21" s="6">
         <v>43678</v>
       </c>
@@ -1413,7 +1701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="57.6">
       <c r="A22" s="6">
         <v>44044</v>
       </c>
@@ -1440,6 +1728,52 @@
       </c>
       <c r="I22" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="72">
+      <c r="A23" s="6">
+        <v>44044</v>
+      </c>
+      <c r="B23" s="2">
+        <v>680</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="57.6">
+      <c r="A24" s="6">
+        <v>44044</v>
+      </c>
+      <c r="B24" s="2">
+        <v>88</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF7AC9B3-383F-4AF1-8DF4-7F8517BD047A}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE415B03-C1F5-4115-B67B-3F88561402E9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="134">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -672,6 +672,270 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Three pointers from the end → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(m+n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove Duplicated from Sorted Array </t>
+  </si>
+  <si>
+    <t>Two Pointers / Read-Write Pointer</t>
+  </si>
+  <si>
+    <t>Use a Set to store unique elements → O(n) time, O(n) space</t>
+  </si>
+  <si>
+    <t>Create a separate array/list of unique elements → O(n) time, O(n) space</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two pointers + in-place overwrite → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Sorting + Two Pointers + Duplicate Handling</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check every triplet → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n³)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extra space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HashSet/HashMap-based 2Sum for each fixed element → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> average time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sort + fix one element + two pointers → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extra space </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(excluding output)</t>
     </r>
   </si>
 </sst>
@@ -679,7 +943,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,6 +976,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1124,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1756,7 +2028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="57.6">
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="57.6">
       <c r="A24" s="6">
         <v>44044</v>
       </c>
@@ -1766,14 +2038,69 @@
       <c r="C24" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="8" t="s">
         <v>122</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="57.6">
+      <c r="A25" s="6">
+        <v>44409</v>
+      </c>
+      <c r="B25" s="2">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="57.6">
+      <c r="A26" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B26" s="2">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE415B03-C1F5-4115-B67B-3F88561402E9}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB9BCA23-A9D5-49B9-B2A8-58F7C0AE755F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="135">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -937,6 +937,9 @@
       </rPr>
       <t>(excluding output)</t>
     </r>
+  </si>
+  <si>
+    <t>4Sum</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1058,6 +1061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1396,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2103,6 +2107,17 @@
         <v>133</v>
       </c>
     </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="9">
+        <v>45139</v>
+      </c>
+      <c r="B27" s="2">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB9BCA23-A9D5-49B9-B2A8-58F7C0AE755F}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{534B6BA8-0BBD-4344-BF53-CDD4B8B2D5FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="149">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -940,6 +940,468 @@
   </si>
   <si>
     <t>4Sum</t>
+  </si>
+  <si>
+    <t>K-Sum / Sorting + Recursion + Two Pointers</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check every quadruplet → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n⁴)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extra space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fix 2 elements + HashSet/HashMap for remaining 2 → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> average time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sort + K-Sum reduction to 2Sum + Two Pointers → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n³)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> auxiliary space </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(excluding output)</t>
+    </r>
+  </si>
+  <si>
+    <t>Rotate Array</t>
+  </si>
+  <si>
+    <t>Array Reversal / In-place Manipulation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rotate one position at a time → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n·k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use extra array → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reversal algorithm: reverse all → reverse first </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → reverse remaining → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Container With Most Water</t>
+  </si>
+  <si>
+    <t>Two Pointers + Greedy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Check every pair </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>(i,j)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Start from both ends; calculate area and move the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shorter-height pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1061,7 +1523,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1400,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2107,8 +2571,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="9">
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="86.4">
+      <c r="A27" s="6">
         <v>45139</v>
       </c>
       <c r="B27" s="2">
@@ -2116,6 +2580,70 @@
       </c>
       <c r="C27" s="2" t="s">
         <v>134</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="72">
+      <c r="A28" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B28" s="2">
+        <v>189</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="8" customFormat="1" ht="72">
+      <c r="A29" s="9">
+        <v>45505</v>
+      </c>
+      <c r="B29" s="2">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{534B6BA8-0BBD-4344-BF53-CDD4B8B2D5FC}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1138EB-5F84-4511-A0E9-13E279EAA0BE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="159">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -1349,6 +1349,271 @@
         <scheme val="minor"/>
       </rPr>
       <t>shorter-height pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Boats to save People</t>
+  </si>
+  <si>
+    <t>Sorting + Two Pointers + Greedy</t>
+  </si>
+  <si>
+    <t>Frequency/counting approach when weight range is small → depends on constraints</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Try different pairings/boat assignments → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exponential</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the general formulation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sort + two pointers: pair heaviest with lightest when possible, otherwise heaviest goes alone → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n log n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> auxiliary space</t>
+    </r>
+  </si>
+  <si>
+    <t>Trapping Rain Water</t>
+  </si>
+  <si>
+    <t>Two Pointers + Prefix/Suffix Maximum Concept</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For each index, find maximum on left and right → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Prefix + suffix maximum arrays → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Two pointers maintaining </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>maxL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>maxR</t>
     </r>
     <r>
       <rPr>
@@ -1408,7 +1673,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1444,6 +1709,13 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1497,7 +1769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1525,6 +1797,15 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1864,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2645,6 +2926,64 @@
       <c r="G29" s="8" t="s">
         <v>148</v>
       </c>
+      <c r="H29" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="12" customFormat="1" ht="100.8">
+      <c r="A30" s="10">
+        <v>45505</v>
+      </c>
+      <c r="B30" s="2">
+        <v>881</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="57.6">
+      <c r="A31" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B31" s="2">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C1138EB-5F84-4511-A0E9-13E279EAA0BE}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22687B23-B320-4EF0-8F00-C17B51D79415}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="168">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -1624,6 +1624,307 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Contains Dupllcates II</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compare every pair within distance </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n·k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HashMap storing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>value → latest index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sliding window HashSet of at most </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> elements → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> average time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Sliding Window + HashSet</t>
+  </si>
+  <si>
+    <t>Best Time to Buy and Sell Stock</t>
+  </si>
+  <si>
+    <t>Greedy + Prefix Minimum / Two Pointers</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Try every buy/sell pair → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n²)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Track minimum buying price and maximum profit while scanning once → </t>
     </r>
     <r>
       <rPr>
@@ -1673,7 +1974,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1709,13 +2010,6 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1769,7 +2063,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1797,15 +2091,6 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2145,7 +2430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2930,8 +3215,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="12" customFormat="1" ht="100.8">
-      <c r="A30" s="10">
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="100.8">
+      <c r="A30" s="6">
         <v>45505</v>
       </c>
       <c r="B30" s="2">
@@ -2940,16 +3225,16 @@
       <c r="C30" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="8" t="s">
         <v>153</v>
       </c>
       <c r="H30" s="5" t="s">
@@ -2983,6 +3268,52 @@
       </c>
       <c r="I31" s="5" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="72">
+      <c r="A32" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B32" s="2">
+        <v>219</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="8" customFormat="1" ht="72">
+      <c r="A33" s="9">
+        <v>45870</v>
+      </c>
+      <c r="B33" s="2">
+        <v>121</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22687B23-B320-4EF0-8F00-C17B51D79415}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D709122-DA14-4CF3-9F6C-95AA4F0A9B9C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="173">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -1957,6 +1957,153 @@
         <scheme val="minor"/>
       </rPr>
       <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Longest substring without repeating characters</t>
+  </si>
+  <si>
+    <t>Variable Sliding Window + HashMap</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Generate every substring and check for duplicates → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n³)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sliding window + HashSet → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sliding window + HashMap storing last index → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(k)</t>
     </r>
     <r>
       <rPr>
@@ -2430,7 +2577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3293,7 +3440,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="8" customFormat="1" ht="72">
+    <row r="33" spans="1:9" s="8" customFormat="1" ht="72">
       <c r="A33" s="9">
         <v>45870</v>
       </c>
@@ -3314,6 +3461,35 @@
       </c>
       <c r="G33" s="8" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="72">
+      <c r="A34" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9b136d2c56d9b2c/Desktop/DSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D709122-DA14-4CF3-9F6C-95AA4F0A9B9C}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{5B3B84DD-17E3-420C-95BC-4F0D31426A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EAC5C78-8489-4AF4-A629-A96A763A14B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ED054C5-D629-4E7E-86E7-A39364DEBD8D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="178">
   <si>
     <t>LeetCode No.</t>
   </si>
@@ -2104,6 +2104,153 @@
         <scheme val="minor"/>
       </rPr>
       <t>O(k)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <t>Longest Repeating Character Replacement</t>
+  </si>
+  <si>
+    <t>Variable Sliding Window + Frequency Array</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Generate every substring and calculate replacements → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n² × 26)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≈ O(n²)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sliding Window + HashMap/Frequency Map → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(26n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ≈ O(n), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(26)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> space</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sliding Window + Frequency Array + maintain maximum frequency → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> time, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(26)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>O(1)</t>
     </r>
     <r>
       <rPr>
@@ -2577,7 +2724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C388EE0F-AE8C-48B7-A754-047DB474560D}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3492,6 +3639,35 @@
         <v>13</v>
       </c>
     </row>
+    <row r="35" spans="1:9" s="8" customFormat="1" ht="86.4">
+      <c r="A35" s="9">
+        <v>46235</v>
+      </c>
+      <c r="B35" s="2">
+        <v>424</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-92" windowWidth="23251" windowHeight="12452" activeTab="0" tabRatio="600"/>
+    <workbookView xWindow="-75" yWindow="-61" windowWidth="23221" windowHeight="12421" activeTab="0" tabRatio="600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="194">
   <si>
     <t>Date</t>
   </si>
@@ -2415,22 +2415,70 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>Minimum size subarray sum</t>
+  </si>
+  <si>
+    <t>Variable Sliding Window + Running Sum</t>
+  </si>
+  <si>
+    <t>Generate all subarrays and calculate sums → O(n²) time, O(1) space</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="1"/>
+      </rPr>
+      <t>Prefix Sum + Binary Search → O(n log n) time, O(n) space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sliding Window: expand right, shrink while sum &gt;= target → O(n) time, O(1) space</t>
+  </si>
+  <si>
+    <t>Find K closest element</t>
+  </si>
+  <si>
+    <t>Sorted Array + Two Pointers + Binary Search on Window</t>
+  </si>
+  <si>
+    <t>Calculate distance for every element and sort/select → O(n log n)</t>
+  </si>
+  <si>
+    <t>Binary Search for insertion position + Two Pointers expanding outward → O(log n + k)</t>
+  </si>
+  <si>
+    <t>Binary Search directly for the starting index of the k-size window → O(log(n-k) + k)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="mmm/yy"/>
+  <numFmts count="8">
+    <numFmt numFmtId="176" formatCode="[$-409]mmm/yy;@"/>
     <numFmt numFmtId="177" formatCode="0%"/>
     <numFmt numFmtId="178" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="181" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="d/mmm"/>
+    <numFmt numFmtId="182" formatCode="[$-409]d/mmm;@"/>
+    <numFmt numFmtId="183" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="22">
+  <fonts count="39" x14ac:knownFonts="39">
     <font>
       <sz val="11.0"/>
       <name val="Aptos Narrow"/>
@@ -2565,12 +2613,122 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9.0"/>
+      <color rgb="FF9C0006"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF006100"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF9C6500"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <name val="Aptos Narrow"/>
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="64">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2763,8 +2921,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC0DA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D79B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1A0C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BACC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2796,6 +3140,128 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFA7BFDE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF4F81BD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2924,7 +3390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" applyAlignment="1" xfId="0">
@@ -2954,7 +3420,6 @@
     <xf numFmtId="176" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
@@ -3001,15 +3466,59 @@
     <xf numFmtId="179" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="180" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="181" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="182" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
-    <xf numFmtId="182" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="33" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="22" applyFont="1" fillId="34" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="23" applyFont="1" fillId="35" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="24" applyFont="1" fillId="36" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="37" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="26" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="27" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="15" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="29" applyFont="1" fillId="36" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="30" applyFont="1" fillId="38" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="39" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="19" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="20" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="21" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="35" applyFont="1" fillId="0" borderId="22" applyBorder="1" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="40" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="41" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="42" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="43" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="44" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="45" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="46" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="47" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="48" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="49" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="50" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="36" applyFont="1" fillId="51" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="52" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="53" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="54" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="55" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="56" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="57" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="58" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="59" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="60" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="61" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="62" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="37" applyFont="1" fillId="63" applyFill="1" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="180" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="183" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3025,7 +3534,7 @@
   <sheetPr>
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.0"/>
@@ -3942,7 +4451,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="9" customFormat="1" ht="63.74903" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="10">
+      <c r="A35" s="7">
         <v>46235.0</v>
       </c>
       <c r="B35" s="3">
@@ -3971,11 +4480,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="59.999084" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="59">
-        <v>46261</v>
-      </c>
+      <c r="A36" s="7"/>
       <c r="B36" s="3">
-        <v>567</v>
+        <v>567.0</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>178</v>
@@ -3983,13 +4490,13 @@
       <c r="D36" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="E36" s="62" t="s">
+      <c r="E36" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="5" t="s">
         <v>182</v>
       </c>
       <c r="H36" s="6" t="s">
@@ -3997,6 +4504,53 @@
       </c>
       <c r="I36" s="9" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="63.74903" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="7"/>
+      <c r="B37" s="3">
+        <v>209.0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="50.99922" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="3">
+        <v>658</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="106" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="106" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="106" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" s="106" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/DSATracking.xlsx
+++ b/DSATracking.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-61" windowWidth="23221" windowHeight="12421" activeTab="0" tabRatio="600"/>
+    <workbookView xWindow="-60" yWindow="-46" windowWidth="23206" windowHeight="12406" activeTab="0" tabRatio="600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="205">
   <si>
     <t>Date</t>
   </si>
@@ -2462,6 +2462,39 @@
   </si>
   <si>
     <t>Binary Search directly for the starting index of the k-size window → O(log(n-k) + k)</t>
+  </si>
+  <si>
+    <t>Minimum Window Substring</t>
+  </si>
+  <si>
+    <t>Variable Sliding Window + Frequency Map + Have/Need</t>
+  </si>
+  <si>
+    <t>Generate every substring and check whether it contains all required characters → O(n² × charset)</t>
+  </si>
+  <si>
+    <t>Sliding Window + frequency map, repeatedly compare frequencies → O(n × charset)</t>
+  </si>
+  <si>
+    <t>Sliding Window + frequency map + have/need → O(n + m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High priority </t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+  </si>
+  <si>
+    <t>Fixed Sliding Window + Monotonic Deque</t>
+  </si>
+  <si>
+    <t>Scan every window to find maximum → O(nk)</t>
+  </si>
+  <si>
+    <t>Heap / Priority Queue with lazy removal → O(n log k)</t>
+  </si>
+  <si>
+    <t>Monotonic Deque storing indices → O(n)</t>
   </si>
 </sst>
 </file>
@@ -3390,7 +3423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
     <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="1" applyBorder="1" applyAlignment="1" xfId="0">
@@ -3519,6 +3552,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3534,7 +3570,7 @@
   <sheetPr>
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="9.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.0"/>
@@ -4535,22 +4571,74 @@
     </row>
     <row r="38" spans="1:7" ht="50.99922" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="3">
-        <v>658</v>
+        <v>658.0</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="106" t="s">
+      <c r="D38" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E38" s="106" t="s">
+      <c r="E38" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F38" s="106" t="s">
+      <c r="F38" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G38" s="106" t="s">
+      <c r="G38" s="5" t="s">
         <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="76.49883" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="3">
+        <v>76</v>
+      </c>
+      <c r="C39" s="106" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="106" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" s="106" t="s">
+        <v>197</v>
+      </c>
+      <c r="G39" s="106" t="s">
+        <v>198</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="38.249416" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="109">
+        <v>239</v>
+      </c>
+      <c r="C40" s="106" t="s">
+        <v>200</v>
+      </c>
+      <c r="D40" s="106" t="s">
+        <v>201</v>
+      </c>
+      <c r="E40" s="106" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" s="106" t="s">
+        <v>203</v>
+      </c>
+      <c r="G40" s="106" t="s">
+        <v>204</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
